--- a/storage/app/Sumbu Grafik.xlsx
+++ b/storage/app/Sumbu Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -552,9 +552,196 @@
         <v>280</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>VEI</v>
+      </c>
+      <c r="B10" t="str">
+        <v>5600</v>
+      </c>
+      <c r="C10" t="str">
+        <v>11650</v>
+      </c>
+      <c r="D10" t="str">
+        <v>125</v>
+      </c>
+      <c r="E10" t="str">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>VER</v>
+      </c>
+      <c r="B11" t="str">
+        <v>6800</v>
+      </c>
+      <c r="C11" t="str">
+        <v>15000</v>
+      </c>
+      <c r="D11" t="str">
+        <v>120</v>
+      </c>
+      <c r="E11" t="str">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>OSI</v>
+      </c>
+      <c r="B12" t="str">
+        <v>4850</v>
+      </c>
+      <c r="C12" t="str">
+        <v>9650</v>
+      </c>
+      <c r="D12" t="str">
+        <v>120</v>
+      </c>
+      <c r="E12" t="str">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>OEM</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4850</v>
+      </c>
+      <c r="C13" t="str">
+        <v>9650</v>
+      </c>
+      <c r="D13" t="str">
+        <v>120</v>
+      </c>
+      <c r="E13" t="str">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BAU</v>
+      </c>
+      <c r="B14" t="str">
+        <v>100</v>
+      </c>
+      <c r="C14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="str">
+        <v>200</v>
+      </c>
+      <c r="E14" t="str">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BKU</v>
+      </c>
+      <c r="B15" t="str">
+        <v>100</v>
+      </c>
+      <c r="C15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="D15" t="str">
+        <v>200</v>
+      </c>
+      <c r="E15" t="str">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>BSA</v>
+      </c>
+      <c r="B16" t="str">
+        <v>100</v>
+      </c>
+      <c r="C16" t="str">
+        <v>1000</v>
+      </c>
+      <c r="D16" t="str">
+        <v>200</v>
+      </c>
+      <c r="E16" t="str">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BGI</v>
+      </c>
+      <c r="B17" t="str">
+        <v>100</v>
+      </c>
+      <c r="C17" t="str">
+        <v>1000</v>
+      </c>
+      <c r="D17" t="str">
+        <v>200</v>
+      </c>
+      <c r="E17" t="str">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">PAH </v>
+      </c>
+      <c r="B18" t="str">
+        <v>445</v>
+      </c>
+      <c r="C18" t="str">
+        <v>1945</v>
+      </c>
+      <c r="D18" t="str">
+        <v>200</v>
+      </c>
+      <c r="E18" t="str">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PST</v>
+      </c>
+      <c r="B19" t="str">
+        <v>505</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2200</v>
+      </c>
+      <c r="D19" t="str">
+        <v>200</v>
+      </c>
+      <c r="E19" t="str">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>PRA</v>
+      </c>
+      <c r="B20" t="str">
+        <v>505</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2200</v>
+      </c>
+      <c r="D20" t="str">
+        <v>200</v>
+      </c>
+      <c r="E20" t="str">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Sumbu Grafik.xlsx
+++ b/storage/app/Sumbu Grafik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SPIL\Bunker Bahan Bakar\Dashboard Tool Box\ToolBox\ToolBox\storage\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE486E06-231E-4737-A90C-ABD54C5978FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A39944-0F81-4364-887E-0B567B6B5437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
   <si>
     <t>VESSEL</t>
   </si>
@@ -185,6 +185,21 @@
   </si>
   <si>
     <t>HAP</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>AKA</t>
+  </si>
+  <si>
+    <t>DER</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>KAA</t>
   </si>
 </sst>
 </file>
@@ -561,10 +576,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -581,7 +596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -598,7 +613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -615,7 +630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -632,7 +647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -649,7 +664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -666,7 +681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -683,7 +698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -700,7 +715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -717,7 +732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -734,7 +749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -751,7 +766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -768,7 +783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -785,7 +800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -802,7 +817,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -819,7 +834,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -836,7 +851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -853,7 +868,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -870,7 +885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -887,7 +902,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -904,7 +919,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -921,7 +936,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -938,7 +953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -955,7 +970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -970,6 +985,91 @@
       </c>
       <c r="E24" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25">
+        <v>610</v>
+      </c>
+      <c r="C25">
+        <v>2650</v>
+      </c>
+      <c r="D25">
+        <v>200</v>
+      </c>
+      <c r="E25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26">
+        <v>610</v>
+      </c>
+      <c r="C26">
+        <v>2650</v>
+      </c>
+      <c r="D26">
+        <v>200</v>
+      </c>
+      <c r="E26">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27">
+        <v>610</v>
+      </c>
+      <c r="C27">
+        <v>2650</v>
+      </c>
+      <c r="D27">
+        <v>200</v>
+      </c>
+      <c r="E27">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28">
+        <v>610</v>
+      </c>
+      <c r="C28">
+        <v>2650</v>
+      </c>
+      <c r="D28">
+        <v>200</v>
+      </c>
+      <c r="E28">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29">
+        <v>610</v>
+      </c>
+      <c r="C29">
+        <v>2650</v>
+      </c>
+      <c r="D29">
+        <v>200</v>
+      </c>
+      <c r="E29">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/storage/app/Sumbu Grafik.xlsx
+++ b/storage/app/Sumbu Grafik.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SPIL\Bunker Bahan Bakar\Dashboard Tool Box\ToolBox\ToolBox\storage\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A39944-0F81-4364-887E-0B567B6B5437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885805C9-C517-4AFB-951A-EC88306EE9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
   <si>
     <t>VESSEL</t>
   </si>
@@ -67,9 +67,6 @@
     <t>135</t>
   </si>
   <si>
-    <t>2425</t>
-  </si>
-  <si>
     <t>200</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
     <t>PRA</t>
   </si>
   <si>
+    <t>HAN</t>
+  </si>
+  <si>
     <t>1700</t>
   </si>
   <si>
@@ -175,21 +175,27 @@
     <t>176</t>
   </si>
   <si>
+    <t>HAP</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
     <t>HAY</t>
   </si>
   <si>
-    <t>HAN</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>HAP</t>
-  </si>
-  <si>
     <t>FOR</t>
   </si>
   <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>2650</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>AKA</t>
   </si>
   <si>
@@ -200,6 +206,120 @@
   </si>
   <si>
     <t>KAA</t>
+  </si>
+  <si>
+    <t>OJA</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>2340</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>ORU</t>
+  </si>
+  <si>
+    <t>ASR</t>
+  </si>
+  <si>
+    <t>ASN</t>
+  </si>
+  <si>
+    <t>ASG</t>
+  </si>
+  <si>
+    <t>APE</t>
+  </si>
+  <si>
+    <t>REN</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>2430</t>
+  </si>
+  <si>
+    <t>PFA</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>PBE</t>
+  </si>
+  <si>
+    <t>739</t>
+  </si>
+  <si>
+    <t>821</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>OGA</t>
+  </si>
+  <si>
+    <t>6900</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>LUZ</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>ODI</t>
+  </si>
+  <si>
+    <t>HJE</t>
+  </si>
+  <si>
+    <t>4300</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>HSJ</t>
+  </si>
+  <si>
+    <t>2400</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>PSM</t>
+  </si>
+  <si>
+    <t>PNN</t>
   </si>
 </sst>
 </file>
@@ -576,10 +696,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -613,7 +733,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -630,128 +750,128 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -766,15 +886,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
@@ -783,15 +903,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
         <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
@@ -800,128 +920,128 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
         <v>34</v>
       </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
         <v>33</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
         <v>34</v>
       </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
         <v>34</v>
       </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>38</v>
       </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
         <v>41</v>
       </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="D19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>52</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
@@ -936,9 +1056,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>47</v>
@@ -953,9 +1073,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -970,9 +1090,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -987,95 +1107,300 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
         <v>55</v>
       </c>
-      <c r="B25">
-        <v>610</v>
-      </c>
-      <c r="C25">
-        <v>2650</v>
-      </c>
-      <c r="D25">
-        <v>200</v>
-      </c>
-      <c r="E25">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
         <v>56</v>
       </c>
-      <c r="B26">
-        <v>610</v>
-      </c>
-      <c r="C26">
-        <v>2650</v>
-      </c>
-      <c r="D26">
-        <v>200</v>
-      </c>
-      <c r="E26">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
         <v>57</v>
       </c>
-      <c r="B27">
-        <v>610</v>
-      </c>
-      <c r="C27">
-        <v>2650</v>
-      </c>
-      <c r="D27">
-        <v>200</v>
-      </c>
-      <c r="E27">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28">
-        <v>610</v>
-      </c>
-      <c r="C28">
-        <v>2650</v>
-      </c>
-      <c r="D28">
-        <v>200</v>
-      </c>
-      <c r="E28">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29">
-        <v>610</v>
-      </c>
-      <c r="C29">
-        <v>2650</v>
-      </c>
-      <c r="D29">
-        <v>200</v>
-      </c>
-      <c r="E29">
-        <v>250</v>
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E20 B24:E24 B21:E21 B22:E22 B23:E23" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E3 A10:E45 A4:A9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Sumbu Grafik.xlsx
+++ b/storage/app/Sumbu Grafik.xlsx
@@ -897,16 +897,16 @@
         <v>OJA</v>
       </c>
       <c r="B30" t="str">
-        <v>1170</v>
+        <v>5400</v>
       </c>
       <c r="C30" t="str">
-        <v>2340</v>
+        <v>12600</v>
       </c>
       <c r="D30" t="str">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E30" t="str">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31">
@@ -914,16 +914,16 @@
         <v>ORU</v>
       </c>
       <c r="B31" t="str">
-        <v>1170</v>
+        <v>5400</v>
       </c>
       <c r="C31" t="str">
-        <v>2340</v>
+        <v>12600</v>
       </c>
       <c r="D31" t="str">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E31" t="str">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32">

--- a/storage/app/Sumbu Grafik.xlsx
+++ b/storage/app/Sumbu Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1201,9 +1201,26 @@
         <v>206</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TIT</v>
+      </c>
+      <c r="B51" t="str">
+        <v>6800</v>
+      </c>
+      <c r="C51" t="str">
+        <v>15000</v>
+      </c>
+      <c r="D51" t="str">
+        <v>120</v>
+      </c>
+      <c r="E51" t="str">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Sumbu Grafik.xlsx
+++ b/storage/app/Sumbu Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1218,9 +1218,26 @@
         <v>130</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>HSG</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2400</v>
+      </c>
+      <c r="C52" t="str">
+        <v>11000</v>
+      </c>
+      <c r="D52" t="str">
+        <v>127</v>
+      </c>
+      <c r="E52" t="str">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E52"/>
   </ignoredErrors>
 </worksheet>
 </file>